--- a/development/rocksdb/self_rd_e5/saved01/structured_log_data.xlsx
+++ b/development/rocksdb/self_rd_e5/saved01/structured_log_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L37"/>
+  <dimension ref="A1:L41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -837,64 +837,68 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>log6112</t>
+          <t>log7011</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>12932703898</v>
+        <v>12466822873</v>
       </c>
       <c r="C11" t="n">
-        <v>8366267</v>
-      </c>
-      <c r="D11" t="inlineStr"/>
+        <v>8241820</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.0011</v>
+      </c>
       <c r="E11" t="n">
-        <v>17684495316</v>
-      </c>
-      <c r="F11" t="inlineStr"/>
+        <v>14646587666</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.0025</v>
+      </c>
       <c r="G11" t="n">
-        <v>262002863756</v>
+        <v>115071790804</v>
       </c>
       <c r="H11" t="n">
-        <v>1073899830594</v>
+        <v>905723253204</v>
       </c>
       <c r="I11" t="n">
-        <v>5656</v>
+        <v>3974</v>
       </c>
       <c r="J11" t="n">
-        <v>340</v>
+        <v>201</v>
       </c>
       <c r="K11" t="n">
-        <v>1417078</v>
+        <v>845392</v>
       </c>
       <c r="L11" t="n">
-        <v>57173139.33</v>
+        <v>34505592.67</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>log6212</t>
+          <t>log6112</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>12458594972</v>
+        <v>12932703898</v>
       </c>
       <c r="C12" t="n">
-        <v>8357102</v>
+        <v>8366267</v>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="n">
-        <v>14818842392</v>
+        <v>17684495316</v>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="n">
-        <v>203955867517</v>
+        <v>262002863756</v>
       </c>
       <c r="H12" t="n">
-        <v>1026153676381</v>
+        <v>1073899830594</v>
       </c>
       <c r="I12" t="n">
-        <v>1840</v>
+        <v>5656</v>
       </c>
       <c r="J12" t="n">
         <v>340</v>
@@ -903,534 +907,530 @@
         <v>1417078</v>
       </c>
       <c r="L12" t="n">
-        <v>54697161.67</v>
+        <v>57173139.33</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>log6312</t>
+          <t>log6212</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>12625159129</v>
+        <v>12458594972</v>
       </c>
       <c r="C13" t="n">
-        <v>8215847</v>
+        <v>8357102</v>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="n">
-        <v>14732394448</v>
+        <v>14818842392</v>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="n">
-        <v>124213346271</v>
+        <v>203955867517</v>
       </c>
       <c r="H13" t="n">
-        <v>923115012461</v>
+        <v>1026153676381</v>
       </c>
       <c r="I13" t="n">
-        <v>37744</v>
+        <v>1840</v>
       </c>
       <c r="J13" t="n">
-        <v>285.33</v>
+        <v>340</v>
       </c>
       <c r="K13" t="n">
-        <v>1187296.67</v>
+        <v>1417078</v>
       </c>
       <c r="L13" t="n">
-        <v>47930738.67</v>
+        <v>54697161.67</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>log6412</t>
+          <t>log6312</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>12525213916</v>
+        <v>12625159129</v>
       </c>
       <c r="C14" t="n">
-        <v>8256363</v>
+        <v>8215847</v>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="n">
-        <v>14335551518</v>
+        <v>14732394448</v>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="n">
-        <v>744377839</v>
+        <v>124213346271</v>
       </c>
       <c r="H14" t="n">
-        <v>798809040365</v>
+        <v>923115012461</v>
       </c>
       <c r="I14" t="n">
-        <v>72336</v>
+        <v>37744</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>285.33</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>1187296.67</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>47930738.67</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>log6512</t>
+          <t>log6412</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>12504824156</v>
+        <v>12525213916</v>
       </c>
       <c r="C15" t="n">
-        <v>8303864</v>
-      </c>
-      <c r="D15" t="n">
-        <v>-1</v>
-      </c>
+        <v>8256363</v>
+      </c>
+      <c r="D15" t="inlineStr"/>
       <c r="E15" t="n">
-        <v>14379546458</v>
-      </c>
-      <c r="F15" t="n">
-        <v>-1</v>
-      </c>
+        <v>14335551518</v>
+      </c>
+      <c r="F15" t="inlineStr"/>
       <c r="G15" t="n">
-        <v>204074200825</v>
+        <v>744377839</v>
       </c>
       <c r="H15" t="n">
-        <v>997303547471</v>
+        <v>798809040365</v>
       </c>
       <c r="I15" t="n">
-        <v>1822</v>
+        <v>72336</v>
       </c>
       <c r="J15" t="n">
-        <v>340</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>1417078</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>56279114.67</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>log6612</t>
+          <t>log6512</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>12695491025</v>
+        <v>12504824156</v>
       </c>
       <c r="C16" t="n">
-        <v>8293936</v>
+        <v>8303864</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E16" t="n">
-        <v>14841014051</v>
+        <v>14379546458</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G16" t="n">
-        <v>133188672547</v>
+        <v>204074200825</v>
       </c>
       <c r="H16" t="n">
-        <v>924919594629</v>
+        <v>997303547471</v>
       </c>
       <c r="I16" t="n">
-        <v>9091</v>
+        <v>1822</v>
       </c>
       <c r="J16" t="n">
-        <v>290.33</v>
+        <v>340</v>
       </c>
       <c r="K16" t="n">
-        <v>1208318.33</v>
+        <v>1417078</v>
       </c>
       <c r="L16" t="n">
-        <v>50760788</v>
+        <v>56279114.67</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>log6712</t>
+          <t>log6612</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>12599648903</v>
+        <v>12695491025</v>
       </c>
       <c r="C17" t="n">
-        <v>8310289</v>
+        <v>8293936</v>
       </c>
       <c r="D17" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>14674095097</v>
+        <v>14841014051</v>
       </c>
       <c r="F17" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>207728720562</v>
+        <v>133188672547</v>
       </c>
       <c r="H17" t="n">
-        <v>1001068432122</v>
+        <v>924919594629</v>
       </c>
       <c r="I17" t="n">
-        <v>1164</v>
+        <v>9091</v>
       </c>
       <c r="J17" t="n">
-        <v>340</v>
+        <v>290.33</v>
       </c>
       <c r="K17" t="n">
-        <v>1417078</v>
+        <v>1208318.33</v>
       </c>
       <c r="L17" t="n">
-        <v>57562339</v>
+        <v>50760788</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>log6812</t>
+          <t>log6712</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>12502313757</v>
+        <v>12599648903</v>
       </c>
       <c r="C18" t="n">
-        <v>8309153</v>
+        <v>8310289</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0021</v>
+        <v>-1</v>
       </c>
       <c r="E18" t="n">
-        <v>14743299928</v>
+        <v>14674095097</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0483</v>
+        <v>-1</v>
       </c>
       <c r="G18" t="n">
-        <v>156403235045</v>
+        <v>207728720562</v>
       </c>
       <c r="H18" t="n">
-        <v>949956059138</v>
+        <v>1001068432122</v>
       </c>
       <c r="I18" t="n">
-        <v>3574</v>
+        <v>1164</v>
       </c>
       <c r="J18" t="n">
-        <v>302.67</v>
+        <v>340</v>
       </c>
       <c r="K18" t="n">
-        <v>1260165.67</v>
+        <v>1417078</v>
       </c>
       <c r="L18" t="n">
-        <v>52313161</v>
+        <v>57562339</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>log6912</t>
+          <t>log6812</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>12639717008</v>
+        <v>12502313757</v>
       </c>
       <c r="C19" t="n">
-        <v>8245992</v>
+        <v>8309153</v>
       </c>
       <c r="D19" t="n">
-        <v>-1</v>
+        <v>0.0021</v>
       </c>
       <c r="E19" t="n">
-        <v>14859092592</v>
+        <v>14743299928</v>
       </c>
       <c r="F19" t="n">
-        <v>-1</v>
+        <v>0.0483</v>
       </c>
       <c r="G19" t="n">
-        <v>207767672277</v>
+        <v>156403235045</v>
       </c>
       <c r="H19" t="n">
-        <v>1001849471913</v>
+        <v>949956059138</v>
       </c>
       <c r="I19" t="n">
-        <v>1494</v>
+        <v>3574</v>
       </c>
       <c r="J19" t="n">
-        <v>340</v>
+        <v>302.67</v>
       </c>
       <c r="K19" t="n">
-        <v>1417078</v>
+        <v>1260165.67</v>
       </c>
       <c r="L19" t="n">
-        <v>58857436.33</v>
+        <v>52313161</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>log6113</t>
+          <t>log6912</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>13236733773</v>
+        <v>12639717008</v>
       </c>
       <c r="C20" t="n">
-        <v>8227978</v>
-      </c>
-      <c r="D20" t="inlineStr"/>
+        <v>8245992</v>
+      </c>
+      <c r="D20" t="n">
+        <v>-1</v>
+      </c>
       <c r="E20" t="n">
-        <v>17384830201</v>
-      </c>
-      <c r="F20" t="inlineStr"/>
+        <v>14859092592</v>
+      </c>
+      <c r="F20" t="n">
+        <v>-1</v>
+      </c>
       <c r="G20" t="n">
-        <v>258599350624</v>
+        <v>207767672277</v>
       </c>
       <c r="H20" t="n">
-        <v>1066058087021</v>
+        <v>1001849471913</v>
       </c>
       <c r="I20" t="n">
-        <v>7056</v>
+        <v>1494</v>
       </c>
       <c r="J20" t="n">
-        <v>226.33</v>
+        <v>340</v>
       </c>
       <c r="K20" t="n">
-        <v>946853.67</v>
+        <v>1417078</v>
       </c>
       <c r="L20" t="n">
-        <v>40140962.33</v>
+        <v>58857436.33</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>log6213</t>
+          <t>log7012</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>12866760766</v>
+        <v>12658598699</v>
       </c>
       <c r="C21" t="n">
-        <v>8302350</v>
-      </c>
-      <c r="D21" t="inlineStr"/>
+        <v>8254224</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0.0019</v>
+      </c>
       <c r="E21" t="n">
-        <v>14170528633</v>
-      </c>
-      <c r="F21" t="inlineStr"/>
+        <v>14920090934</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.0014</v>
+      </c>
       <c r="G21" t="n">
-        <v>194557911572</v>
+        <v>134668184367</v>
       </c>
       <c r="H21" t="n">
-        <v>1014279109362</v>
+        <v>926385823591</v>
       </c>
       <c r="I21" t="n">
-        <v>2048</v>
+        <v>6448</v>
       </c>
       <c r="J21" t="n">
-        <v>226.33</v>
+        <v>290.33</v>
       </c>
       <c r="K21" t="n">
-        <v>946853.67</v>
+        <v>1208318.33</v>
       </c>
       <c r="L21" t="n">
-        <v>39148826.67</v>
+        <v>49974312.67</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>log6313</t>
+          <t>log6113</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>13176745697</v>
+        <v>13236733773</v>
       </c>
       <c r="C22" t="n">
-        <v>8301324</v>
+        <v>8227978</v>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="n">
-        <v>14222823684</v>
+        <v>17384830201</v>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="n">
-        <v>100967784478</v>
+        <v>258599350624</v>
       </c>
       <c r="H22" t="n">
-        <v>896371501309</v>
+        <v>1066058087021</v>
       </c>
       <c r="I22" t="n">
-        <v>64336</v>
+        <v>7056</v>
       </c>
       <c r="J22" t="n">
-        <v>187.33</v>
+        <v>226.33</v>
       </c>
       <c r="K22" t="n">
-        <v>784345.67</v>
+        <v>946853.67</v>
       </c>
       <c r="L22" t="n">
-        <v>32119638.33</v>
+        <v>40140962.33</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>log6413</t>
+          <t>log6213</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>12697305852</v>
+        <v>12866760766</v>
       </c>
       <c r="C23" t="n">
-        <v>8362642</v>
+        <v>8302350</v>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="n">
-        <v>12824021439</v>
+        <v>14170528633</v>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="n">
-        <v>717318708</v>
+        <v>194557911572</v>
       </c>
       <c r="H23" t="n">
-        <v>792980245273</v>
+        <v>1014279109362</v>
       </c>
       <c r="I23" t="n">
-        <v>109392</v>
+        <v>2048</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>226.33</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>946853.67</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>39148826.67</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>log6513</t>
+          <t>log6313</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>12884216537</v>
+        <v>13176745697</v>
       </c>
       <c r="C24" t="n">
-        <v>8296867</v>
-      </c>
-      <c r="D24" t="n">
-        <v>-1</v>
-      </c>
+        <v>8301324</v>
+      </c>
+      <c r="D24" t="inlineStr"/>
       <c r="E24" t="n">
-        <v>14316604403</v>
-      </c>
-      <c r="F24" t="n">
-        <v>-1</v>
-      </c>
+        <v>14222823684</v>
+      </c>
+      <c r="F24" t="inlineStr"/>
       <c r="G24" t="n">
-        <v>195846792939</v>
+        <v>100967784478</v>
       </c>
       <c r="H24" t="n">
-        <v>984367565255</v>
+        <v>896371501309</v>
       </c>
       <c r="I24" t="n">
-        <v>2324</v>
+        <v>64336</v>
       </c>
       <c r="J24" t="n">
-        <v>226.33</v>
+        <v>187.33</v>
       </c>
       <c r="K24" t="n">
-        <v>946853.67</v>
+        <v>784345.67</v>
       </c>
       <c r="L24" t="n">
-        <v>37602832.67</v>
+        <v>32119638.33</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>log6613</t>
+          <t>log6413</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>12919948135</v>
+        <v>12697305852</v>
       </c>
       <c r="C25" t="n">
-        <v>8273309</v>
-      </c>
-      <c r="D25" t="n">
+        <v>8362642</v>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="n">
+        <v>12824021439</v>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="n">
+        <v>717318708</v>
+      </c>
+      <c r="H25" t="n">
+        <v>792980245273</v>
+      </c>
+      <c r="I25" t="n">
+        <v>109392</v>
+      </c>
+      <c r="J25" t="n">
         <v>0</v>
       </c>
-      <c r="E25" t="n">
-        <v>14572327897</v>
-      </c>
-      <c r="F25" t="n">
+      <c r="K25" t="n">
         <v>0</v>
       </c>
-      <c r="G25" t="n">
-        <v>123964374676</v>
-      </c>
-      <c r="H25" t="n">
-        <v>910845055027</v>
-      </c>
-      <c r="I25" t="n">
-        <v>14630</v>
-      </c>
-      <c r="J25" t="n">
-        <v>193</v>
-      </c>
-      <c r="K25" t="n">
-        <v>808156.67</v>
-      </c>
       <c r="L25" t="n">
-        <v>32639338.67</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>log6713</t>
+          <t>log6513</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>12895738403</v>
+        <v>12884216537</v>
       </c>
       <c r="C26" t="n">
-        <v>8071639</v>
+        <v>8296867</v>
       </c>
       <c r="D26" t="n">
         <v>-1</v>
       </c>
       <c r="E26" t="n">
-        <v>14313805658</v>
+        <v>14316604403</v>
       </c>
       <c r="F26" t="n">
         <v>-1</v>
       </c>
       <c r="G26" t="n">
-        <v>200373160267</v>
+        <v>195846792939</v>
       </c>
       <c r="H26" t="n">
-        <v>989305693270</v>
+        <v>984367565255</v>
       </c>
       <c r="I26" t="n">
-        <v>1498</v>
+        <v>2324</v>
       </c>
       <c r="J26" t="n">
         <v>226.33</v>
@@ -1439,78 +1439,78 @@
         <v>946853.67</v>
       </c>
       <c r="L26" t="n">
-        <v>37077774.67</v>
+        <v>37602832.67</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>log6813</t>
+          <t>log6613</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>12913216701</v>
+        <v>12919948135</v>
       </c>
       <c r="C27" t="n">
-        <v>8159282</v>
+        <v>8273309</v>
       </c>
       <c r="D27" t="n">
-        <v>0.0036</v>
+        <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>14447539047</v>
+        <v>14572327897</v>
       </c>
       <c r="F27" t="n">
-        <v>0.0506</v>
+        <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>148532129323</v>
+        <v>123964374676</v>
       </c>
       <c r="H27" t="n">
-        <v>939020449110</v>
+        <v>910845055027</v>
       </c>
       <c r="I27" t="n">
-        <v>5569</v>
+        <v>14630</v>
       </c>
       <c r="J27" t="n">
-        <v>202</v>
+        <v>193</v>
       </c>
       <c r="K27" t="n">
-        <v>845975.67</v>
+        <v>808156.67</v>
       </c>
       <c r="L27" t="n">
-        <v>31615808</v>
+        <v>32639338.67</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>log6913</t>
+          <t>log6713</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>13077190234</v>
+        <v>12895738403</v>
       </c>
       <c r="C28" t="n">
-        <v>8178279</v>
+        <v>8071639</v>
       </c>
       <c r="D28" t="n">
         <v>-1</v>
       </c>
       <c r="E28" t="n">
-        <v>14417269322</v>
+        <v>14313805658</v>
       </c>
       <c r="F28" t="n">
         <v>-1</v>
       </c>
       <c r="G28" t="n">
-        <v>197838822643</v>
+        <v>200373160267</v>
       </c>
       <c r="H28" t="n">
-        <v>987097151378</v>
+        <v>989305693270</v>
       </c>
       <c r="I28" t="n">
-        <v>1912</v>
+        <v>1498</v>
       </c>
       <c r="J28" t="n">
         <v>226.33</v>
@@ -1519,182 +1519,190 @@
         <v>946853.67</v>
       </c>
       <c r="L28" t="n">
-        <v>40552377.33</v>
+        <v>37077774.67</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>log6114</t>
+          <t>log6813</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>13589279116</v>
+        <v>12913216701</v>
       </c>
       <c r="C29" t="n">
-        <v>9421319</v>
-      </c>
-      <c r="D29" t="inlineStr"/>
+        <v>8159282</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0.0036</v>
+      </c>
       <c r="E29" t="n">
-        <v>17446840709</v>
-      </c>
-      <c r="F29" t="inlineStr"/>
+        <v>14447539047</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0.0506</v>
+      </c>
       <c r="G29" t="n">
-        <v>263188543498</v>
+        <v>148532129323</v>
       </c>
       <c r="H29" t="n">
-        <v>1065876621959</v>
+        <v>939020449110</v>
       </c>
       <c r="I29" t="n">
-        <v>6440</v>
+        <v>5569</v>
       </c>
       <c r="J29" t="n">
-        <v>281.67</v>
+        <v>202</v>
       </c>
       <c r="K29" t="n">
-        <v>1165684</v>
+        <v>845975.67</v>
       </c>
       <c r="L29" t="n">
-        <v>50298520</v>
+        <v>31615808</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>log6214</t>
+          <t>log6913</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>13162843312</v>
+        <v>13077190234</v>
       </c>
       <c r="C30" t="n">
-        <v>9592469</v>
-      </c>
-      <c r="D30" t="inlineStr"/>
+        <v>8178279</v>
+      </c>
+      <c r="D30" t="n">
+        <v>-1</v>
+      </c>
       <c r="E30" t="n">
-        <v>14526602521</v>
-      </c>
-      <c r="F30" t="inlineStr"/>
+        <v>14417269322</v>
+      </c>
+      <c r="F30" t="n">
+        <v>-1</v>
+      </c>
       <c r="G30" t="n">
-        <v>200735635649</v>
+        <v>197838822643</v>
       </c>
       <c r="H30" t="n">
-        <v>1016592873175</v>
+        <v>987097151378</v>
       </c>
       <c r="I30" t="n">
-        <v>2320</v>
+        <v>1912</v>
       </c>
       <c r="J30" t="n">
-        <v>281.67</v>
+        <v>226.33</v>
       </c>
       <c r="K30" t="n">
-        <v>1165684</v>
+        <v>946853.67</v>
       </c>
       <c r="L30" t="n">
-        <v>47038773.67</v>
+        <v>40552377.33</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>log6314</t>
+          <t>log7013</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>12991075469</v>
+        <v>13266969293</v>
       </c>
       <c r="C31" t="n">
-        <v>9603997</v>
-      </c>
-      <c r="D31" t="inlineStr"/>
+        <v>8187584</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0.0035</v>
+      </c>
       <c r="E31" t="n">
-        <v>14164770714</v>
-      </c>
-      <c r="F31" t="inlineStr"/>
+        <v>14357278797</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0.001</v>
+      </c>
       <c r="G31" t="n">
-        <v>119294443318</v>
+        <v>125590096903</v>
       </c>
       <c r="H31" t="n">
-        <v>911650972138</v>
+        <v>912135429958</v>
       </c>
       <c r="I31" t="n">
-        <v>86144</v>
+        <v>10293</v>
       </c>
       <c r="J31" t="n">
-        <v>233.67</v>
+        <v>193</v>
       </c>
       <c r="K31" t="n">
-        <v>966724</v>
+        <v>808156.67</v>
       </c>
       <c r="L31" t="n">
-        <v>39096797.67</v>
+        <v>32696248.67</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>log6414</t>
+          <t>log6114</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>13009149098</v>
+        <v>13589279116</v>
       </c>
       <c r="C32" t="n">
-        <v>9540457</v>
+        <v>9421319</v>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="n">
-        <v>13611392919</v>
+        <v>17446840709</v>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="n">
-        <v>720437553</v>
+        <v>263188543498</v>
       </c>
       <c r="H32" t="n">
-        <v>791450427366</v>
+        <v>1065876621959</v>
       </c>
       <c r="I32" t="n">
-        <v>155488</v>
+        <v>6440</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>281.67</v>
       </c>
       <c r="K32" t="n">
-        <v>0</v>
+        <v>1165684</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>50298520</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>log6514</t>
+          <t>log6214</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>13401427720</v>
+        <v>13162843312</v>
       </c>
       <c r="C33" t="n">
-        <v>9529830</v>
-      </c>
-      <c r="D33" t="n">
-        <v>-1</v>
-      </c>
+        <v>9592469</v>
+      </c>
+      <c r="D33" t="inlineStr"/>
       <c r="E33" t="n">
-        <v>14788106340</v>
-      </c>
-      <c r="F33" t="n">
-        <v>-1</v>
-      </c>
+        <v>14526602521</v>
+      </c>
+      <c r="F33" t="inlineStr"/>
       <c r="G33" t="n">
-        <v>201833805235</v>
+        <v>200735635649</v>
       </c>
       <c r="H33" t="n">
-        <v>992586427127</v>
+        <v>1016592873175</v>
       </c>
       <c r="I33" t="n">
-        <v>2098</v>
+        <v>2320</v>
       </c>
       <c r="J33" t="n">
         <v>281.67</v>
@@ -1703,167 +1711,319 @@
         <v>1165684</v>
       </c>
       <c r="L33" t="n">
-        <v>47897023.67</v>
+        <v>47038773.67</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>log6614</t>
+          <t>log6314</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>13107116106</v>
+        <v>12991075469</v>
       </c>
       <c r="C34" t="n">
-        <v>9551217</v>
-      </c>
-      <c r="D34" t="n">
-        <v>0</v>
-      </c>
+        <v>9603997</v>
+      </c>
+      <c r="D34" t="inlineStr"/>
       <c r="E34" t="n">
-        <v>14878175283</v>
-      </c>
-      <c r="F34" t="n">
-        <v>0</v>
-      </c>
+        <v>14164770714</v>
+      </c>
+      <c r="F34" t="inlineStr"/>
       <c r="G34" t="n">
-        <v>141432066254</v>
+        <v>119294443318</v>
       </c>
       <c r="H34" t="n">
-        <v>928705019419</v>
+        <v>911650972138</v>
       </c>
       <c r="I34" t="n">
-        <v>14258</v>
+        <v>86144</v>
       </c>
       <c r="J34" t="n">
-        <v>246.67</v>
+        <v>233.67</v>
       </c>
       <c r="K34" t="n">
-        <v>1021354</v>
+        <v>966724</v>
       </c>
       <c r="L34" t="n">
-        <v>42271371.67</v>
+        <v>39096797.67</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>log6714</t>
+          <t>log6414</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>13002801521</v>
+        <v>13009149098</v>
       </c>
       <c r="C35" t="n">
-        <v>9517341</v>
-      </c>
-      <c r="D35" t="n">
-        <v>-1</v>
-      </c>
+        <v>9540457</v>
+      </c>
+      <c r="D35" t="inlineStr"/>
       <c r="E35" t="n">
-        <v>13103652760</v>
-      </c>
-      <c r="F35" t="n">
-        <v>-1</v>
-      </c>
+        <v>13611392919</v>
+      </c>
+      <c r="F35" t="inlineStr"/>
       <c r="G35" t="n">
-        <v>195942643712</v>
+        <v>720437553</v>
       </c>
       <c r="H35" t="n">
-        <v>981737149572</v>
+        <v>791450427366</v>
       </c>
       <c r="I35" t="n">
-        <v>1361</v>
+        <v>155488</v>
       </c>
       <c r="J35" t="n">
-        <v>281.67</v>
+        <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>1165684</v>
+        <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>43876768.67</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>log6814</t>
+          <t>log6514</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>13045007458</v>
+        <v>13401427720</v>
       </c>
       <c r="C36" t="n">
-        <v>9596328</v>
+        <v>9529830</v>
       </c>
       <c r="D36" t="n">
-        <v>0.0037</v>
+        <v>-1</v>
       </c>
       <c r="E36" t="n">
-        <v>14563017682</v>
+        <v>14788106340</v>
       </c>
       <c r="F36" t="n">
-        <v>0.0372</v>
+        <v>-1</v>
       </c>
       <c r="G36" t="n">
-        <v>157527662069</v>
+        <v>201833805235</v>
       </c>
       <c r="H36" t="n">
-        <v>947114060265</v>
+        <v>992586427127</v>
       </c>
       <c r="I36" t="n">
-        <v>5326</v>
+        <v>2098</v>
       </c>
       <c r="J36" t="n">
-        <v>263</v>
+        <v>281.67</v>
       </c>
       <c r="K36" t="n">
-        <v>1087212.33</v>
+        <v>1165684</v>
       </c>
       <c r="L36" t="n">
-        <v>44045501</v>
+        <v>47897023.67</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
+          <t>log6614</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>13107116106</v>
+      </c>
+      <c r="C37" t="n">
+        <v>9551217</v>
+      </c>
+      <c r="D37" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" t="n">
+        <v>14878175283</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" t="n">
+        <v>141432066254</v>
+      </c>
+      <c r="H37" t="n">
+        <v>928705019419</v>
+      </c>
+      <c r="I37" t="n">
+        <v>14258</v>
+      </c>
+      <c r="J37" t="n">
+        <v>246.67</v>
+      </c>
+      <c r="K37" t="n">
+        <v>1021354</v>
+      </c>
+      <c r="L37" t="n">
+        <v>42271371.67</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>log6714</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>13002801521</v>
+      </c>
+      <c r="C38" t="n">
+        <v>9517341</v>
+      </c>
+      <c r="D38" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E38" t="n">
+        <v>13103652760</v>
+      </c>
+      <c r="F38" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G38" t="n">
+        <v>195942643712</v>
+      </c>
+      <c r="H38" t="n">
+        <v>981737149572</v>
+      </c>
+      <c r="I38" t="n">
+        <v>1361</v>
+      </c>
+      <c r="J38" t="n">
+        <v>281.67</v>
+      </c>
+      <c r="K38" t="n">
+        <v>1165684</v>
+      </c>
+      <c r="L38" t="n">
+        <v>43876768.67</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>log6814</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>13045007458</v>
+      </c>
+      <c r="C39" t="n">
+        <v>9596328</v>
+      </c>
+      <c r="D39" t="n">
+        <v>0.0037</v>
+      </c>
+      <c r="E39" t="n">
+        <v>14563017682</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0.0372</v>
+      </c>
+      <c r="G39" t="n">
+        <v>157527662069</v>
+      </c>
+      <c r="H39" t="n">
+        <v>947114060265</v>
+      </c>
+      <c r="I39" t="n">
+        <v>5326</v>
+      </c>
+      <c r="J39" t="n">
+        <v>263</v>
+      </c>
+      <c r="K39" t="n">
+        <v>1087212.33</v>
+      </c>
+      <c r="L39" t="n">
+        <v>44045501</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
           <t>log6914</t>
         </is>
       </c>
-      <c r="B37" t="n">
+      <c r="B40" t="n">
         <v>13289891129</v>
       </c>
-      <c r="C37" t="n">
+      <c r="C40" t="n">
         <v>9248700</v>
       </c>
-      <c r="D37" t="n">
-        <v>-1</v>
-      </c>
-      <c r="E37" t="n">
+      <c r="D40" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E40" t="n">
         <v>14723761840</v>
       </c>
-      <c r="F37" t="n">
-        <v>-1</v>
-      </c>
-      <c r="G37" t="n">
+      <c r="F40" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G40" t="n">
         <v>203326804337</v>
       </c>
-      <c r="H37" t="n">
+      <c r="H40" t="n">
         <v>992222658329</v>
       </c>
-      <c r="I37" t="n">
+      <c r="I40" t="n">
         <v>1730</v>
       </c>
-      <c r="J37" t="n">
+      <c r="J40" t="n">
         <v>281.67</v>
       </c>
-      <c r="K37" t="n">
+      <c r="K40" t="n">
         <v>1165684</v>
       </c>
-      <c r="L37" t="n">
+      <c r="L40" t="n">
         <v>45897708.33</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>log7014</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>13354707712</v>
+      </c>
+      <c r="C41" t="n">
+        <v>9722088</v>
+      </c>
+      <c r="D41" t="n">
+        <v>0.0035</v>
+      </c>
+      <c r="E41" t="n">
+        <v>14764837744</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0.0007</v>
+      </c>
+      <c r="G41" t="n">
+        <v>142245242677</v>
+      </c>
+      <c r="H41" t="n">
+        <v>932105944845</v>
+      </c>
+      <c r="I41" t="n">
+        <v>10000</v>
+      </c>
+      <c r="J41" t="n">
+        <v>247.67</v>
+      </c>
+      <c r="K41" t="n">
+        <v>1025558</v>
+      </c>
+      <c r="L41" t="n">
+        <v>41295446</v>
       </c>
     </row>
   </sheetData>
